--- a/diseases/d242/2010-2014.xlsx
+++ b/diseases/d242/2010-2014.xlsx
@@ -3216,11 +3216,6 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>SER_SI_ECDC_LGV_ANNUAL</t>
@@ -3238,12 +3233,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -3253,11 +3243,6 @@
       </c>
       <c r="AT19" t="n">
         <v>1</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3323,17 +3308,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3358,48 +3343,26 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2010-01-01</t>
+          <t>2011-01-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2010-01</t>
+          <t>2011-01</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.1902409732583246</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>Chlamydia infection, lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_BE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3407,64 +3370,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN20" t="b">
-        <v>1</v>
-      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -3472,27 +3377,17 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_BE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT20" t="n">
         <v>1</v>
       </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -3500,7 +3395,7 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -3520,7 +3415,7 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
@@ -3562,12 +3457,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3601,17 +3496,17 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1902409732583246</v>
+        <v>0</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_LGV_ANNUAL</t>
+          <t>SER_CY_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3631,7 +3526,7 @@
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_LGV_ANNUAL</t>
+          <t>SER_CY_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT21" t="n">
@@ -3644,7 +3539,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -3664,7 +3559,7 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
@@ -3706,12 +3601,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3745,17 +3640,17 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.05716729752367464</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_LGV_ANNUAL</t>
+          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3775,7 +3670,7 @@
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_LGV_ANNUAL</t>
+          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT22" t="n">
@@ -3788,7 +3683,7 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -3808,7 +3703,7 @@
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
@@ -3850,12 +3745,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3889,17 +3784,17 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="O23" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="R23" t="n">
-        <v>0.05716729752367464</v>
+        <v>0.5205669728258655</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
+          <t>SER_DK_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3919,7 +3814,7 @@
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
+          <t>SER_DK_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT23" t="n">
@@ -3932,7 +3827,7 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -3952,7 +3847,7 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
@@ -3994,12 +3889,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -4033,17 +3928,17 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5205669728258655</v>
+        <v>0</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LGV_ANNUAL</t>
+          <t>SER_EE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -4063,7 +3958,7 @@
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LGV_ANNUAL</t>
+          <t>SER_EE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT24" t="n">
@@ -4076,7 +3971,7 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -4096,7 +3991,7 @@
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
@@ -4138,12 +4033,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4177,17 +4072,17 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>0.05567679693614298</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_LGV_ANNUAL</t>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4207,7 +4102,7 @@
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_LGV_ANNUAL</t>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT25" t="n">
@@ -4215,42 +4110,42 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4177,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4321,17 +4216,17 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>186</v>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
+        <v>186</v>
       </c>
       <c r="R26" t="n">
-        <v>0.05567679693614298</v>
+        <v>0.2918389726063152</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4351,7 +4246,7 @@
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT26" t="n">
@@ -4359,42 +4254,42 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -4426,12 +4321,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4465,17 +4360,17 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>186</v>
+        <v>408</v>
       </c>
       <c r="O27" t="n">
-        <v>186</v>
+        <v>408</v>
       </c>
       <c r="R27" t="n">
-        <v>0.2918389726063152</v>
+        <v>0.6424257441850767</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_LGV_ANNUAL</t>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4495,7 +4390,7 @@
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_LGV_ANNUAL</t>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT27" t="n">
@@ -4508,7 +4403,7 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -4528,7 +4423,7 @@
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
@@ -4570,12 +4465,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4609,17 +4504,17 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>408</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>408</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.6424257441850767</v>
+        <v>0</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4639,7 +4534,7 @@
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT28" t="n">
@@ -4652,7 +4547,7 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -4672,7 +4567,7 @@
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
@@ -4714,12 +4609,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4763,7 +4658,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4783,7 +4678,7 @@
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT29" t="n">
@@ -4791,42 +4686,42 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
     </row>
@@ -4858,12 +4753,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4897,17 +4792,17 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>0.01822161071600999</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+          <t>SER_IT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4927,7 +4822,7 @@
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+          <t>SER_IT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT30" t="n">
@@ -4935,42 +4830,42 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -5002,12 +4897,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -5041,17 +4936,17 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0.01822161071600999</v>
+        <v>0</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_LGV_ANNUAL</t>
+          <t>SER_LU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -5071,7 +4966,7 @@
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_LGV_ANNUAL</t>
+          <t>SER_LU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT31" t="n">
@@ -5084,7 +4979,7 @@
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
@@ -5104,7 +4999,7 @@
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
@@ -5146,12 +5041,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -5195,7 +5090,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LGV_ANNUAL</t>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5215,7 +5110,7 @@
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LGV_ANNUAL</t>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT32" t="n">
@@ -5228,7 +5123,7 @@
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -5248,7 +5143,7 @@
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
@@ -5290,12 +5185,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5339,7 +5234,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+          <t>SER_MT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5359,7 +5254,7 @@
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+          <t>SER_MT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT33" t="n">
@@ -5372,7 +5267,7 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
@@ -5392,7 +5287,7 @@
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
@@ -5434,12 +5329,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5473,17 +5368,17 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>0.415404208768625</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_LGV_ANNUAL</t>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5503,7 +5398,7 @@
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_LGV_ANNUAL</t>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT34" t="n">
@@ -5516,7 +5411,7 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
@@ -5536,7 +5431,7 @@
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
@@ -5578,12 +5473,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5617,17 +5512,17 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0.415404208768625</v>
+        <v>0</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+          <t>SER_PL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5647,7 +5542,7 @@
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+          <t>SER_PL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT35" t="n">
@@ -5660,7 +5555,7 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -5680,7 +5575,7 @@
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
@@ -5722,12 +5617,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5771,7 +5666,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_LGV_ANNUAL</t>
+          <t>SER_SE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5791,7 +5686,7 @@
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_LGV_ANNUAL</t>
+          <t>SER_SE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT36" t="n">
@@ -5799,42 +5694,42 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -5866,12 +5761,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5915,7 +5810,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>SER_SE_ECDC_LGV_ANNUAL</t>
+          <t>SER_SI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5935,7 +5830,7 @@
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>SER_SE_ECDC_LGV_ANNUAL</t>
+          <t>SER_SI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT37" t="n">
@@ -5943,42 +5838,42 @@
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -6010,12 +5905,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -6040,31 +5935,26 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2011-01-01</t>
+          <t>2012-01-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2011-01</t>
+          <t>2012-01</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0.2070669613139497</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_BE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -6079,27 +5969,17 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ38" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_BE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT38" t="n">
         <v>1</v>
       </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -6107,7 +5987,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -6127,7 +6007,7 @@
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
@@ -6164,17 +6044,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6199,12 +6079,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2011-01-01</t>
+          <t>2012-01-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2011-01</t>
+          <t>2012-01</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6213,34 +6093,12 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>Chlamydia infection, lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_CY_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6248,64 +6106,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG39" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN39" t="b">
-        <v>1</v>
-      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -6313,27 +6113,17 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ39" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_CY_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT39" t="n">
         <v>1</v>
       </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV39" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -6341,7 +6131,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -6361,7 +6151,7 @@
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
@@ -6403,12 +6193,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6442,17 +6232,17 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="O40" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="R40" t="n">
-        <v>0.2070669613139497</v>
+        <v>0.08565444996281169</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_LGV_ANNUAL</t>
+          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6472,7 +6262,7 @@
       </c>
       <c r="AS40" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_LGV_ANNUAL</t>
+          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT40" t="n">
@@ -6485,7 +6275,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -6505,7 +6295,7 @@
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
@@ -6547,12 +6337,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -6586,17 +6376,17 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>0.4291909580552571</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_LGV_ANNUAL</t>
+          <t>SER_DK_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6616,7 +6406,7 @@
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_LGV_ANNUAL</t>
+          <t>SER_DK_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT41" t="n">
@@ -6629,7 +6419,7 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -6649,7 +6439,7 @@
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
@@ -6691,12 +6481,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6730,17 +6520,17 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0.08565444996281169</v>
+        <v>0</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
+          <t>SER_EE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6760,7 +6550,7 @@
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
+          <t>SER_EE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT42" t="n">
@@ -6773,7 +6563,7 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -6793,7 +6583,7 @@
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
@@ -6835,12 +6625,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6874,17 +6664,17 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="O43" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="R43" t="n">
-        <v>0.4291909580552571</v>
+        <v>0.09235364463961437</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LGV_ANNUAL</t>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6904,7 +6694,7 @@
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LGV_ANNUAL</t>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT43" t="n">
@@ -6912,42 +6702,42 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -6979,12 +6769,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -7018,17 +6808,17 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>0.2903597495634672</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_LGV_ANNUAL</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -7048,7 +6838,7 @@
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_LGV_ANNUAL</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT44" t="n">
@@ -7061,7 +6851,7 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -7081,7 +6871,7 @@
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
@@ -7123,12 +6913,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7162,17 +6952,17 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0.09235364463961437</v>
+        <v>0</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -7192,7 +6982,7 @@
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT45" t="n">
@@ -7200,42 +6990,42 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -7267,12 +7057,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7306,17 +7096,17 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.2903597495634672</v>
+        <v>0</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_LGV_ANNUAL</t>
+          <t>SER_GR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -7336,7 +7126,7 @@
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_LGV_ANNUAL</t>
+          <t>SER_GR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT46" t="n">
@@ -7349,7 +7139,7 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -7369,7 +7159,7 @@
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
@@ -7411,12 +7201,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7460,7 +7250,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+          <t>SER_HR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7480,7 +7270,7 @@
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+          <t>SER_HR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT47" t="n">
@@ -7493,7 +7283,7 @@
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
@@ -7513,7 +7303,7 @@
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
@@ -7555,12 +7345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7594,17 +7384,17 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>0.01008407801728472</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>SER_GR_ECDC_LGV_ANNUAL</t>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7624,7 +7414,7 @@
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>SER_GR_ECDC_LGV_ANNUAL</t>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT48" t="n">
@@ -7637,7 +7427,7 @@
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -7657,7 +7447,7 @@
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
@@ -7699,12 +7489,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7738,17 +7528,17 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>0.06521551990247236</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_LGV_ANNUAL</t>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7768,7 +7558,7 @@
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_LGV_ANNUAL</t>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT49" t="n">
@@ -7776,42 +7566,42 @@
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
     </row>
@@ -7843,12 +7633,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7882,17 +7672,17 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="O50" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="R50" t="n">
-        <v>0.01008407801728472</v>
+        <v>0.04460486409434821</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+          <t>SER_IT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7912,7 +7702,7 @@
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+          <t>SER_IT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT50" t="n">
@@ -7925,7 +7715,7 @@
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
@@ -7945,7 +7735,7 @@
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
@@ -7987,12 +7777,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -8026,17 +7816,17 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0.06521551990247236</v>
+        <v>0</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+          <t>SER_LU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -8056,7 +7846,7 @@
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+          <t>SER_LU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT51" t="n">
@@ -8064,42 +7854,42 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -8131,12 +7921,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8170,17 +7960,17 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0.04460486409434821</v>
+        <v>0</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_LGV_ANNUAL</t>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -8200,7 +7990,7 @@
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_LGV_ANNUAL</t>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT52" t="n">
@@ -8213,7 +8003,7 @@
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
@@ -8233,7 +8023,7 @@
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
@@ -8275,12 +8065,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8324,7 +8114,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LGV_ANNUAL</t>
+          <t>SER_MT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -8344,7 +8134,7 @@
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LGV_ANNUAL</t>
+          <t>SER_MT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT53" t="n">
@@ -8357,7 +8147,7 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
@@ -8377,7 +8167,7 @@
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
@@ -8419,12 +8209,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8458,17 +8248,17 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.123250526220702</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8488,7 +8278,7 @@
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT54" t="n">
@@ -8501,7 +8291,7 @@
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
@@ -8521,7 +8311,7 @@
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
@@ -8563,12 +8353,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8612,7 +8402,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_LGV_ANNUAL</t>
+          <t>SER_PL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8632,7 +8422,7 @@
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_LGV_ANNUAL</t>
+          <t>SER_PL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT55" t="n">
@@ -8645,7 +8435,7 @@
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
@@ -8665,7 +8455,7 @@
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
@@ -8707,12 +8497,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8746,17 +8536,17 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.123250526220702</v>
+        <v>0</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+          <t>SER_SE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8776,7 +8566,7 @@
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+          <t>SER_SE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT56" t="n">
@@ -8784,42 +8574,42 @@
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -8851,12 +8641,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -8900,7 +8690,7 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_LGV_ANNUAL</t>
+          <t>SER_SI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8920,7 +8710,7 @@
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_LGV_ANNUAL</t>
+          <t>SER_SI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT57" t="n">
@@ -8933,7 +8723,7 @@
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
@@ -8953,7 +8743,7 @@
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
@@ -8995,12 +8785,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -9025,26 +8815,26 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2012-01-01</t>
+          <t>2013-01-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2012-01</t>
+          <t>2013-01</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>0.430096890076912</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>SER_SE_ECDC_LGV_ANNUAL</t>
+          <t>SER_BE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -9064,7 +8854,7 @@
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>SER_SE_ECDC_LGV_ANNUAL</t>
+          <t>SER_BE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT58" t="n">
@@ -9072,42 +8862,42 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -9139,12 +8929,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -9169,12 +8959,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2012-01-01</t>
+          <t>2013-01-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2012-01</t>
+          <t>2013-01</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -9186,14 +8976,9 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_CY_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -9208,27 +8993,17 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ59" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_CY_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT59" t="n">
         <v>1</v>
       </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV59" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -9236,7 +9011,7 @@
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
@@ -9256,7 +9031,7 @@
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
@@ -9293,17 +9068,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9328,48 +9103,26 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2012-01-01</t>
+          <t>2013-01-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2012-01</t>
+          <t>2013-01</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.07610956447490941</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>Chlamydia infection, lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -9377,64 +9130,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD60" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE60" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG60" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN60" t="b">
-        <v>1</v>
-      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -9442,27 +9137,17 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT60" t="n">
         <v>1</v>
       </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV60" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -9470,7 +9155,7 @@
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
@@ -9490,7 +9175,7 @@
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
@@ -9532,12 +9217,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9571,17 +9256,17 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="O61" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="R61" t="n">
-        <v>0.430096890076912</v>
+        <v>0.5698683025448626</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_LGV_ANNUAL</t>
+          <t>SER_DK_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -9601,7 +9286,7 @@
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_LGV_ANNUAL</t>
+          <t>SER_DK_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT61" t="n">
@@ -9614,7 +9299,7 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
@@ -9634,7 +9319,7 @@
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
@@ -9676,12 +9361,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -9725,7 +9410,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_LGV_ANNUAL</t>
+          <t>SER_EE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -9745,7 +9430,7 @@
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_LGV_ANNUAL</t>
+          <t>SER_EE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT62" t="n">
@@ -9758,7 +9443,7 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
@@ -9778,7 +9463,7 @@
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
@@ -9820,12 +9505,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -9859,17 +9544,17 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R63" t="n">
-        <v>0.07610956447490941</v>
+        <v>0.1286988746018838</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -9889,7 +9574,7 @@
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT63" t="n">
@@ -9897,42 +9582,42 @@
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -9964,12 +9649,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -10003,17 +9688,17 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>32</v>
+        <v>331</v>
       </c>
       <c r="O64" t="n">
-        <v>32</v>
+        <v>331</v>
       </c>
       <c r="R64" t="n">
-        <v>0.5698683025448626</v>
+        <v>0.5140730686375762</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LGV_ANNUAL</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -10033,7 +9718,7 @@
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LGV_ANNUAL</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT64" t="n">
@@ -10046,7 +9731,7 @@
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
@@ -10066,7 +9751,7 @@
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
@@ -10108,12 +9793,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -10157,7 +9842,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_LGV_ANNUAL</t>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -10177,7 +9862,7 @@
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_LGV_ANNUAL</t>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT65" t="n">
@@ -10190,7 +9875,7 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
@@ -10210,7 +9895,7 @@
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
@@ -10252,12 +9937,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -10291,17 +9976,17 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>0.1286988746018838</v>
+        <v>0</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+          <t>SER_HR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -10321,7 +10006,7 @@
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+          <t>SER_HR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT66" t="n">
@@ -10329,42 +10014,42 @@
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -10396,12 +10081,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -10435,17 +10120,17 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>331</v>
+        <v>2</v>
       </c>
       <c r="O67" t="n">
-        <v>331</v>
+        <v>2</v>
       </c>
       <c r="R67" t="n">
-        <v>0.5140730686375762</v>
+        <v>0.02022378323987334</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_LGV_ANNUAL</t>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -10465,7 +10150,7 @@
       </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_LGV_ANNUAL</t>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT67" t="n">
@@ -10478,7 +10163,7 @@
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
@@ -10498,7 +10183,7 @@
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
@@ -10540,12 +10225,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -10579,17 +10264,17 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>0.108115436581485</v>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -10609,7 +10294,7 @@
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT68" t="n">
@@ -10617,42 +10302,42 @@
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
     </row>
@@ -10684,12 +10369,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -10733,7 +10418,7 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_LGV_ANNUAL</t>
+          <t>SER_IS_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -10753,7 +10438,7 @@
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_LGV_ANNUAL</t>
+          <t>SER_IS_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT69" t="n">
@@ -10761,42 +10446,42 @@
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -10828,12 +10513,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -10867,17 +10552,17 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="O70" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="R70" t="n">
-        <v>0.02022378323987334</v>
+        <v>0.03462268857591499</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+          <t>SER_IT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -10897,7 +10582,7 @@
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+          <t>SER_IT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT70" t="n">
@@ -10910,7 +10595,7 @@
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
@@ -10930,7 +10615,7 @@
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
@@ -10972,12 +10657,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -11011,17 +10696,17 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>0.108115436581485</v>
+        <v>0</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+          <t>SER_LU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -11041,7 +10726,7 @@
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+          <t>SER_LU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT71" t="n">
@@ -11049,42 +10734,42 @@
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -11116,12 +10801,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -11165,7 +10850,7 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>SER_IS_ECDC_LGV_ANNUAL</t>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -11185,7 +10870,7 @@
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>SER_IS_ECDC_LGV_ANNUAL</t>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT72" t="n">
@@ -11193,42 +10878,42 @@
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -11260,12 +10945,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -11299,17 +10984,17 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>0.03462268857591499</v>
+        <v>0.2333981013064459</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_LGV_ANNUAL</t>
+          <t>SER_MT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -11329,7 +11014,7 @@
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_LGV_ANNUAL</t>
+          <t>SER_MT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT73" t="n">
@@ -11342,7 +11027,7 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
@@ -11362,7 +11047,7 @@
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
@@ -11404,12 +11089,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11443,17 +11128,17 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>0.6601024585103503</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LGV_ANNUAL</t>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -11473,7 +11158,7 @@
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LGV_ANNUAL</t>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT74" t="n">
@@ -11486,7 +11171,7 @@
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
@@ -11506,7 +11191,7 @@
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
@@ -11548,12 +11233,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -11597,7 +11282,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+          <t>SER_PL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -11617,7 +11302,7 @@
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+          <t>SER_PL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT75" t="n">
@@ -11630,7 +11315,7 @@
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
@@ -11650,7 +11335,7 @@
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
@@ -11692,12 +11377,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -11731,17 +11416,17 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>0.2333981013064459</v>
+        <v>0</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_LGV_ANNUAL</t>
+          <t>SER_SE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -11761,7 +11446,7 @@
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_LGV_ANNUAL</t>
+          <t>SER_SE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT76" t="n">
@@ -11769,42 +11454,42 @@
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -11836,12 +11521,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -11875,17 +11560,17 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>0.6601024585103503</v>
+        <v>0</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+          <t>SER_SI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -11905,7 +11590,7 @@
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+          <t>SER_SI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT77" t="n">
@@ -11918,7 +11603,7 @@
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
@@ -11938,7 +11623,7 @@
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
@@ -11980,12 +11665,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -12010,26 +11695,26 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2013-01-01</t>
+          <t>2014-01-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2014-01</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>0.5352307143215874</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_LGV_ANNUAL</t>
+          <t>SER_BE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -12049,7 +11734,7 @@
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_LGV_ANNUAL</t>
+          <t>SER_BE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT78" t="n">
@@ -12062,7 +11747,7 @@
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
@@ -12082,7 +11767,7 @@
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
@@ -12124,12 +11809,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -12154,12 +11839,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2013-01-01</t>
+          <t>2014-01-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2014-01</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -12173,7 +11858,7 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>SER_SE_ECDC_LGV_ANNUAL</t>
+          <t>SER_CY_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -12193,7 +11878,7 @@
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>SER_SE_ECDC_LGV_ANNUAL</t>
+          <t>SER_CY_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT79" t="n">
@@ -12201,42 +11886,42 @@
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -12268,12 +11953,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -12298,31 +11983,26 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2013-01-01</t>
+          <t>2014-01-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2014-01</t>
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0.2091806436973325</v>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -12337,27 +12017,17 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ80" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT80" t="n">
         <v>1</v>
       </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV80" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -12365,7 +12035,7 @@
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
@@ -12385,7 +12055,7 @@
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
@@ -12422,17 +12092,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -12457,48 +12127,26 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2013-01-01</t>
+          <t>2014-01-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2014-01</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0.6378687811780515</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>Chlamydia infection, lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_DK_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -12506,64 +12154,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD81" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE81" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF81" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG81" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN81" t="b">
-        <v>1</v>
-      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -12571,27 +12161,17 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ81" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
+          <t>SER_DK_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT81" t="n">
         <v>1</v>
       </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV81" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -12599,7 +12179,7 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
@@ -12619,7 +12199,7 @@
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
@@ -12661,12 +12241,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -12700,17 +12280,17 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>0.5352307143215874</v>
+        <v>0</v>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_LGV_ANNUAL</t>
+          <t>SER_EE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -12730,7 +12310,7 @@
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_LGV_ANNUAL</t>
+          <t>SER_EE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT82" t="n">
@@ -12743,7 +12323,7 @@
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
@@ -12763,7 +12343,7 @@
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
@@ -12805,12 +12385,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -12844,17 +12424,17 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>0.03661874249773513</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_LGV_ANNUAL</t>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -12874,7 +12454,7 @@
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_LGV_ANNUAL</t>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT83" t="n">
@@ -12882,42 +12462,42 @@
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -12949,12 +12529,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -12988,17 +12568,17 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>22</v>
+        <v>377</v>
       </c>
       <c r="O84" t="n">
-        <v>22</v>
+        <v>377</v>
       </c>
       <c r="R84" t="n">
-        <v>0.2091806436973325</v>
+        <v>0.5827569559172573</v>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -13018,7 +12598,7 @@
       </c>
       <c r="AS84" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_LGV_ANNUAL</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT84" t="n">
@@ -13031,7 +12611,7 @@
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
@@ -13051,7 +12631,7 @@
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
@@ -13093,12 +12673,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -13132,17 +12712,17 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>36</v>
+        <v>678</v>
       </c>
       <c r="O85" t="n">
-        <v>36</v>
+        <v>678</v>
       </c>
       <c r="R85" t="n">
-        <v>0.6378687811780515</v>
+        <v>1.045233053941356</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LGV_ANNUAL</t>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -13162,7 +12742,7 @@
       </c>
       <c r="AS85" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_LGV_ANNUAL</t>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT85" t="n">
@@ -13175,7 +12755,7 @@
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
@@ -13195,7 +12775,7 @@
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
@@ -13237,12 +12817,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -13286,7 +12866,7 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_LGV_ANNUAL</t>
+          <t>SER_HR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -13306,7 +12886,7 @@
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_LGV_ANNUAL</t>
+          <t>SER_HR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT86" t="n">
@@ -13319,7 +12899,7 @@
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
@@ -13339,7 +12919,7 @@
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
@@ -13381,12 +12961,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -13420,17 +13000,17 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R87" t="n">
-        <v>0.03661874249773513</v>
+        <v>0.03041719617935682</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -13450,7 +13030,7 @@
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT87" t="n">
@@ -13458,42 +13038,42 @@
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -13525,12 +13105,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -13564,17 +13144,17 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>377</v>
+        <v>39</v>
       </c>
       <c r="O88" t="n">
-        <v>377</v>
+        <v>39</v>
       </c>
       <c r="R88" t="n">
-        <v>0.5827569559172573</v>
+        <v>0.8372263463968194</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_LGV_ANNUAL</t>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -13594,7 +13174,7 @@
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_LGV_ANNUAL</t>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT88" t="n">
@@ -13602,42 +13182,42 @@
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
     </row>
@@ -13669,12 +13249,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -13708,17 +13288,17 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>678</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>678</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>1.045233053941356</v>
+        <v>0</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+          <t>SER_IS_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -13738,7 +13318,7 @@
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+          <t>SER_IS_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT89" t="n">
@@ -13746,42 +13326,42 @@
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -13813,12 +13393,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -13852,17 +13432,17 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>0.01978103335673182</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_LGV_ANNUAL</t>
+          <t>SER_IT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -13882,7 +13462,7 @@
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_LGV_ANNUAL</t>
+          <t>SER_IT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT90" t="n">
@@ -13895,7 +13475,7 @@
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
@@ -13915,7 +13495,7 @@
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
@@ -13957,12 +13537,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -13996,17 +13576,17 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>0.03041719617935682</v>
+        <v>0</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+          <t>SER_LU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -14026,7 +13606,7 @@
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+          <t>SER_LU_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT91" t="n">
@@ -14039,7 +13619,7 @@
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
@@ -14059,7 +13639,7 @@
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
@@ -14101,12 +13681,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -14140,17 +13720,17 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>0.8372263463968194</v>
+        <v>0</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -14170,7 +13750,7 @@
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT92" t="n">
@@ -14178,42 +13758,42 @@
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -14245,12 +13825,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -14294,7 +13874,7 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>SER_IS_ECDC_LGV_ANNUAL</t>
+          <t>SER_MT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -14314,7 +13894,7 @@
       </c>
       <c r="AS93" t="inlineStr">
         <is>
-          <t>SER_IS_ECDC_LGV_ANNUAL</t>
+          <t>SER_MT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT93" t="n">
@@ -14322,42 +13902,42 @@
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -14389,12 +13969,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -14428,17 +14008,17 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>12</v>
+        <v>172</v>
       </c>
       <c r="O94" t="n">
-        <v>12</v>
+        <v>172</v>
       </c>
       <c r="R94" t="n">
-        <v>0.01978103335673182</v>
+        <v>1.009977135468204</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_LGV_ANNUAL</t>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -14458,7 +14038,7 @@
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_LGV_ANNUAL</t>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT94" t="n">
@@ -14471,7 +14051,7 @@
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
@@ -14491,7 +14071,7 @@
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
@@ -14533,12 +14113,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -14582,7 +14162,7 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LGV_ANNUAL</t>
+          <t>SER_PL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -14602,7 +14182,7 @@
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_LGV_ANNUAL</t>
+          <t>SER_PL_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT95" t="n">
@@ -14615,7 +14195,7 @@
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
@@ -14635,7 +14215,7 @@
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
@@ -14677,12 +14257,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -14716,17 +14296,17 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>0.009609657167312347</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+          <t>SER_PT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -14746,7 +14326,7 @@
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+          <t>SER_PT_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT96" t="n">
@@ -14759,7 +14339,7 @@
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
@@ -14779,7 +14359,7 @@
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
@@ -14821,12 +14401,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -14870,7 +14450,7 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_LGV_ANNUAL</t>
+          <t>SER_SE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -14890,7 +14470,7 @@
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_LGV_ANNUAL</t>
+          <t>SER_SE_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT97" t="n">
@@ -14898,42 +14478,42 @@
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -14965,12 +14545,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -15004,17 +14584,17 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>1.009977135468204</v>
+        <v>0</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+          <t>SER_SI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -15034,7 +14614,7 @@
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+          <t>SER_SI_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT98" t="n">
@@ -15047,7 +14627,7 @@
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
@@ -15067,7 +14647,7 @@
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
@@ -15076,831 +14656,6 @@
         </is>
       </c>
       <c r="BC98" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>lymphogranuloma-venereum</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>性病性淋巴肉芽肿</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>2014-01</t>
-        </is>
-      </c>
-      <c r="N99" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" t="n">
-        <v>0</v>
-      </c>
-      <c r="R99" t="n">
-        <v>0</v>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>SER_PL_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP99" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr">
-        <is>
-          <t>SER_PL_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT99" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV99" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW99" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA99" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB99" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC99" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>lymphogranuloma-venereum</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>PT</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>性病性淋巴肉芽肿</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>2014-01</t>
-        </is>
-      </c>
-      <c r="N100" t="n">
-        <v>1</v>
-      </c>
-      <c r="O100" t="n">
-        <v>1</v>
-      </c>
-      <c r="R100" t="n">
-        <v>0.009609657167312347</v>
-      </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>SER_PT_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP100" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr">
-        <is>
-          <t>SER_PT_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT100" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV100" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW100" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY100" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA100" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB100" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC100" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>lymphogranuloma-venereum</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>性病性淋巴肉芽肿</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>2014-01</t>
-        </is>
-      </c>
-      <c r="N101" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0</v>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>SER_SE_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA101" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP101" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr">
-        <is>
-          <t>SER_SE_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT101" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV101" t="inlineStr">
-        <is>
-          <t>fohm_sminet</t>
-        </is>
-      </c>
-      <c r="AW101" t="inlineStr">
-        <is>
-          <t>Sweden Public Health Agency SmiNet</t>
-        </is>
-      </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr">
-        <is>
-          <t>official_html_csv</t>
-        </is>
-      </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>fohm_sminet</t>
-        </is>
-      </c>
-      <c r="BA101" t="inlineStr">
-        <is>
-          <t>Sweden Public Health Agency SmiNet</t>
-        </is>
-      </c>
-      <c r="BB101" t="inlineStr">
-        <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
-        </is>
-      </c>
-      <c r="BC101" t="inlineStr">
-        <is>
-          <t>official_html_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>lymphogranuloma-venereum</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>性病性淋巴肉芽肿</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>2014-01</t>
-        </is>
-      </c>
-      <c r="N102" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" t="n">
-        <v>0</v>
-      </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP102" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ102" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT102" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV102" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW102" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA102" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB102" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC102" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>lymphogranuloma-venereum</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>D242</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>Lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>性病性淋巴肉芽肿</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>2014-01</t>
-        </is>
-      </c>
-      <c r="N103" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" t="n">
-        <v>0</v>
-      </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W103" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X103" t="inlineStr">
-        <is>
-          <t>Chlamydia infection, lymphogranuloma venereum</t>
-        </is>
-      </c>
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
-        </is>
-      </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD103" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE103" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF103" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG103" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN103" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP103" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ103" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_LGV_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT103" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV103" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="AW103" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
-        </is>
-      </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr">
-        <is>
-          <t>official_ecdc_rest_aggregate</t>
-        </is>
-      </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
-      <c r="BA103" t="inlineStr">
-        <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
-        </is>
-      </c>
-      <c r="BB103" t="inlineStr">
-        <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
-        </is>
-      </c>
-      <c r="BC103" t="inlineStr">
         <is>
           <t>official_ecdc_rest_aggregate</t>
         </is>
@@ -16032,7 +14787,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11">
@@ -16052,7 +14807,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -16062,7 +14817,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
